--- a/xsq.xlsx
+++ b/xsq.xlsx
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>r1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,7 +50,87 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>b2</t>
+    <t>redstr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,19,22,23,28,31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,6,9,17,25,28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,13,17,18,25,26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,9,16,22,25,29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,15,20,23,24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-08(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-10(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-12(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-15(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-17(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-05(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,13,21,23,29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,8,10,23,29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-03(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,18,23,25,28,32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-01(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>red_sum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-19(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,11,14,19,22,24</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -82,7 +162,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -90,12 +170,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -397,88 +494,370 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2">
-        <v>2024151</v>
-      </c>
-      <c r="B2">
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2" s="1">
+        <v>2026022</v>
+      </c>
+      <c r="B2" s="1">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1">
+        <v>28</v>
+      </c>
+      <c r="E2" s="1">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1">
+        <f>SUM(B2:G2)</f>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A3" s="1">
+        <v>2026023</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1">
+        <v>6</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K10" si="0">SUM(B3:G3)</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A4" s="1">
+        <v>2026024</v>
+      </c>
+      <c r="B4" s="1">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>2026025</v>
+      </c>
+      <c r="B5" s="1">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>2026026</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
+        <v>2026027</v>
+      </c>
+      <c r="B7" s="1">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
+        <v>2026028</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>2026029</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="I9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>2026030</v>
+      </c>
+      <c r="B10" s="2">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
         <v>10</v>
       </c>
-      <c r="D2">
-        <v>16</v>
-      </c>
-      <c r="E2">
+      <c r="D10" s="2">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>29</v>
-      </c>
-      <c r="G2">
-        <v>32</v>
-      </c>
-      <c r="H2">
+      <c r="E10" s="2">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>2024150</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>14</v>
-      </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
-      <c r="E3">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>26</v>
-      </c>
-      <c r="G3">
-        <v>32</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
+      <c r="I10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/xsq.xlsx
+++ b/xsq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>r1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,6 +131,94 @@
   </si>
   <si>
     <t>10,11,14,19,22,24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-22(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,10,12,13,18,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-24(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,11,18,31,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,6,13,21,28,29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-26(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-29(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,7,13,22,23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,6,12,24,25,32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-31(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-02(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,10,12,15,22,28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-05(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11,22,27,29,31,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-07(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,13,23,25,27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-09(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,17,18,21,25,30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-12(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4,14,22,23,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,8,10,17,19,24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-14(二)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
@@ -604,7 +692,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K10" si="0">SUM(B3:G3)</f>
+        <f t="shared" ref="K3:K21" si="0">SUM(B3:G3)</f>
         <v>74</v>
       </c>
     </row>
@@ -858,6 +946,402 @@
       <c r="K10" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>2026031</v>
+      </c>
+      <c r="B11" s="2">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2">
+        <v>18</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>2026032</v>
+      </c>
+      <c r="B12" s="2">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>2026033</v>
+      </c>
+      <c r="B13" s="2">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>21</v>
+      </c>
+      <c r="H13" s="2">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>2026034</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2">
+        <v>22</v>
+      </c>
+      <c r="H14" s="2">
+        <v>7</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>2026035</v>
+      </c>
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>24</v>
+      </c>
+      <c r="G15" s="2">
+        <v>32</v>
+      </c>
+      <c r="H15" s="2">
+        <v>2</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>2026036</v>
+      </c>
+      <c r="B16" s="2">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2">
+        <v>12</v>
+      </c>
+      <c r="E16" s="2">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2">
+        <v>28</v>
+      </c>
+      <c r="H16" s="2">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>2026037</v>
+      </c>
+      <c r="B17" s="2">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2">
+        <v>33</v>
+      </c>
+      <c r="E17" s="2">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2">
+        <v>29</v>
+      </c>
+      <c r="G17" s="2">
+        <v>27</v>
+      </c>
+      <c r="H17" s="2">
+        <v>12</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="0"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>2026038</v>
+      </c>
+      <c r="B18" s="2">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>2026039</v>
+      </c>
+      <c r="B19" s="2">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2">
+        <v>21</v>
+      </c>
+      <c r="D19" s="2">
+        <v>25</v>
+      </c>
+      <c r="E19" s="2">
+        <v>17</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="2">
+        <f t="shared" si="0"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>2026040</v>
+      </c>
+      <c r="B20" s="2">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2">
+        <v>33</v>
+      </c>
+      <c r="D20" s="2">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3</v>
+      </c>
+      <c r="H20" s="2">
+        <v>4</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>2026041</v>
+      </c>
+      <c r="B21" s="2">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2">
+        <v>24</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2">
+        <v>17</v>
+      </c>
+      <c r="H21" s="2">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/xsq.xlsx
+++ b/xsq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>r1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,6 +219,62 @@
   </si>
   <si>
     <t>2026-04-14(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-16(四)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,7,12,19,24,31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,9,14,16,25,32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-19(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-21(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,14,17,18,22,30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-23(四) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,11,15,17,24,30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,9,10,24,31,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-26(日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-28(二)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7,16,21,24,27,30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,15,18,24,28,33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-30(四)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
@@ -692,7 +748,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K21" si="0">SUM(B3:G3)</f>
+        <f t="shared" ref="K3:K28" si="0">SUM(B3:G3)</f>
         <v>74</v>
       </c>
     </row>
@@ -1342,6 +1398,258 @@
       <c r="K21" s="2">
         <f t="shared" si="0"/>
         <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>2026042</v>
+      </c>
+      <c r="B22" s="2">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2">
+        <v>19</v>
+      </c>
+      <c r="D22" s="2">
+        <v>12</v>
+      </c>
+      <c r="E22" s="2">
+        <v>31</v>
+      </c>
+      <c r="F22" s="2">
+        <v>24</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>2026043</v>
+      </c>
+      <c r="B23" s="2">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>32</v>
+      </c>
+      <c r="F23" s="2">
+        <v>25</v>
+      </c>
+      <c r="G23" s="2">
+        <v>9</v>
+      </c>
+      <c r="H23" s="2">
+        <v>16</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K23" s="2">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>2026044</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>30</v>
+      </c>
+      <c r="D24" s="2">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2">
+        <v>17</v>
+      </c>
+      <c r="F24" s="2">
+        <v>22</v>
+      </c>
+      <c r="G24" s="2">
+        <v>14</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K24" s="2">
+        <f t="shared" si="0"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>2026045</v>
+      </c>
+      <c r="B25" s="2">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2">
+        <v>11</v>
+      </c>
+      <c r="D25" s="2">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>30</v>
+      </c>
+      <c r="F25" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" s="2">
+        <v>17</v>
+      </c>
+      <c r="H25" s="2">
+        <v>15</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="2">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>2026046</v>
+      </c>
+      <c r="B26" s="2">
+        <v>24</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>31</v>
+      </c>
+      <c r="E26" s="2">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2">
+        <v>33</v>
+      </c>
+      <c r="H26" s="2">
+        <v>16</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K26" s="2">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>2026047</v>
+      </c>
+      <c r="B27" s="2">
+        <v>27</v>
+      </c>
+      <c r="C27" s="2">
+        <v>21</v>
+      </c>
+      <c r="D27" s="2">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2">
+        <v>24</v>
+      </c>
+      <c r="F27" s="2">
+        <v>7</v>
+      </c>
+      <c r="G27" s="2">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2">
+        <v>7</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27" s="2">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>2026048</v>
+      </c>
+      <c r="B28" s="2">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2">
+        <v>33</v>
+      </c>
+      <c r="D28" s="2">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2">
+        <v>15</v>
+      </c>
+      <c r="F28" s="2">
+        <v>24</v>
+      </c>
+      <c r="G28" s="2">
+        <v>28</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K28" s="2">
+        <f t="shared" si="0"/>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
